--- a/machine_learning/huigui.xlsx
+++ b/machine_learning/huigui.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="14088"/>
+    <workbookView windowWidth="18348" windowHeight="14075"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+  <si>
+    <t>x,y</t>
+  </si>
   <si>
     <t>x</t>
   </si>
@@ -37,244 +40,244 @@
     <t>y</t>
   </si>
   <si>
-    <t>(1, 111)</t>
-  </si>
-  <si>
-    <t>(2, 240)</t>
-  </si>
-  <si>
-    <t>(3, 56)</t>
-  </si>
-  <si>
-    <t>(4, 208)</t>
-  </si>
-  <si>
-    <t>(5, 275)</t>
-  </si>
-  <si>
-    <t>(6, 119)</t>
-  </si>
-  <si>
-    <t>(7, 215)</t>
-  </si>
-  <si>
-    <t>(8, 109)</t>
-  </si>
-  <si>
-    <t>(9, 260)</t>
-  </si>
-  <si>
-    <t>(10, 176)</t>
-  </si>
-  <si>
-    <t>(11, 318)</t>
-  </si>
-  <si>
-    <t>(12, 144)</t>
-  </si>
-  <si>
-    <t>(13, 273)</t>
-  </si>
-  <si>
-    <t>(14, 211)</t>
-  </si>
-  <si>
-    <t>(15, 327)</t>
-  </si>
-  <si>
-    <t>(16, 190)</t>
-  </si>
-  <si>
-    <t>(17, 286)</t>
-  </si>
-  <si>
-    <t>(18, 157)</t>
-  </si>
-  <si>
-    <t>(19, 331)</t>
-  </si>
-  <si>
-    <t>(20, 225)</t>
-  </si>
-  <si>
-    <t>(21, 243)</t>
-  </si>
-  <si>
-    <t>(22, 371)</t>
-  </si>
-  <si>
-    <t>(23, 221)</t>
-  </si>
-  <si>
-    <t>(24, 339)</t>
-  </si>
-  <si>
-    <t>(25, 198)</t>
-  </si>
-  <si>
-    <t>(26, 384)</t>
-  </si>
-  <si>
-    <t>(27, 278)</t>
-  </si>
-  <si>
-    <t>(28, 374)</t>
-  </si>
-  <si>
-    <t>(29, 235)</t>
-  </si>
-  <si>
-    <t>(30, 353)</t>
-  </si>
-  <si>
-    <t>(31, 448)</t>
-  </si>
-  <si>
-    <t>(32, 297)</t>
-  </si>
-  <si>
-    <t>(33, 415)</t>
-  </si>
-  <si>
-    <t>(34, 276)</t>
-  </si>
-  <si>
-    <t>(35, 394)</t>
-  </si>
-  <si>
-    <t>(36, 271)</t>
-  </si>
-  <si>
-    <t>(37, 428)</t>
-  </si>
-  <si>
-    <t>(38, 355)</t>
-  </si>
-  <si>
-    <t>(39, 473)</t>
-  </si>
-  <si>
-    <t>(40, 323)</t>
-  </si>
-  <si>
-    <t>(41, 441)</t>
-  </si>
-  <si>
-    <t>(42, 290)</t>
-  </si>
-  <si>
-    <t>(43, 486)</t>
-  </si>
-  <si>
-    <t>(44, 380)</t>
-  </si>
-  <si>
-    <t>(45, 476)</t>
-  </si>
-  <si>
-    <t>(46, 337)</t>
-  </si>
-  <si>
-    <t>(47, 455)</t>
-  </si>
-  <si>
-    <t>(48, 393)</t>
-  </si>
-  <si>
-    <t>(49, 511)</t>
-  </si>
-  <si>
-    <t>(50, 372)</t>
-  </si>
-  <si>
-    <t>(51, 400)</t>
-  </si>
-  <si>
-    <t>(52, 564)</t>
-  </si>
-  <si>
-    <t>(53, 434)</t>
-  </si>
-  <si>
-    <t>(54, 563)</t>
-  </si>
-  <si>
-    <t>(55, 457)</t>
-  </si>
-  <si>
-    <t>(56, 542)</t>
-  </si>
-  <si>
-    <t>(57, 414)</t>
-  </si>
-  <si>
-    <t>(58, 532)</t>
-  </si>
-  <si>
-    <t>(59, 402)</t>
-  </si>
-  <si>
-    <t>(60, 555)</t>
-  </si>
-  <si>
-    <t>(61, 449)</t>
-  </si>
-  <si>
-    <t>(62, 611)</t>
-  </si>
-  <si>
-    <t>(63, 483)</t>
-  </si>
-  <si>
-    <t>(64, 557)</t>
-  </si>
-  <si>
-    <t>(65, 484)</t>
-  </si>
-  <si>
-    <t>(66, 624)</t>
-  </si>
-  <si>
-    <t>(67, 518)</t>
-  </si>
-  <si>
-    <t>(68, 660)</t>
-  </si>
-  <si>
-    <t>(69, 519)</t>
-  </si>
-  <si>
-    <t>(70, 637)</t>
-  </si>
-  <si>
-    <t>(71, 487)</t>
-  </si>
-  <si>
-    <t>(72, 616)</t>
-  </si>
-  <si>
-    <t>(73, 510)</t>
-  </si>
-  <si>
-    <t>(74, 650)</t>
-  </si>
-  <si>
-    <t>(75, 577)</t>
-  </si>
-  <si>
-    <t>(76, 695)</t>
-  </si>
-  <si>
-    <t>(77, 567)</t>
-  </si>
-  <si>
-    <t>(78, 685)</t>
-  </si>
-  <si>
-    <t>(79, 590)</t>
-  </si>
-  <si>
-    <t>(80, 732)</t>
+    <t>43,45.2</t>
+  </si>
+  <si>
+    <t>19,27.1</t>
+  </si>
+  <si>
+    <t>61,55.8</t>
+  </si>
+  <si>
+    <t>28,36.7</t>
+  </si>
+  <si>
+    <t>53,48.4</t>
+  </si>
+  <si>
+    <t>35,45.9</t>
+  </si>
+  <si>
+    <t>17,22.3</t>
+  </si>
+  <si>
+    <t>58,52.6</t>
+  </si>
+  <si>
+    <t>24,32.5</t>
+  </si>
+  <si>
+    <t>47,46.8</t>
+  </si>
+  <si>
+    <t>21,28.9</t>
+  </si>
+  <si>
+    <t>63,56.1</t>
+  </si>
+  <si>
+    <t>31,42.0</t>
+  </si>
+  <si>
+    <t>56,51.7</t>
+  </si>
+  <si>
+    <t>40,42.5</t>
+  </si>
+  <si>
+    <t>15,17.8</t>
+  </si>
+  <si>
+    <t>49,49.3</t>
+  </si>
+  <si>
+    <t>26,36.1</t>
+  </si>
+  <si>
+    <t>59,54.2</t>
+  </si>
+  <si>
+    <t>38,41.4</t>
+  </si>
+  <si>
+    <t>45,48.7</t>
+  </si>
+  <si>
+    <t>22,30.2</t>
+  </si>
+  <si>
+    <t>62,55.5</t>
+  </si>
+  <si>
+    <t>33,39.6</t>
+  </si>
+  <si>
+    <t>51,49.9</t>
+  </si>
+  <si>
+    <t>29,38.3</t>
+  </si>
+  <si>
+    <t>18,24.9</t>
+  </si>
+  <si>
+    <t>54,50.2</t>
+  </si>
+  <si>
+    <t>42,47.1</t>
+  </si>
+  <si>
+    <t>25,34.8</t>
+  </si>
+  <si>
+    <t>60,54.5</t>
+  </si>
+  <si>
+    <t>36,42.9</t>
+  </si>
+  <si>
+    <t>48,48.1</t>
+  </si>
+  <si>
+    <t>20,27.4</t>
+  </si>
+  <si>
+    <t>55,51.0</t>
+  </si>
+  <si>
+    <t>39,44.3</t>
+  </si>
+  <si>
+    <t>44,46.5</t>
+  </si>
+  <si>
+    <t>16,21.6</t>
+  </si>
+  <si>
+    <t>64,57.3</t>
+  </si>
+  <si>
+    <t>30,40.1</t>
+  </si>
+  <si>
+    <t>52,50.6</t>
+  </si>
+  <si>
+    <t>34,43.2</t>
+  </si>
+  <si>
+    <t>46,46.9</t>
+  </si>
+  <si>
+    <t>23,33.7</t>
+  </si>
+  <si>
+    <t>57,52.9</t>
+  </si>
+  <si>
+    <t>41,45.7</t>
+  </si>
+  <si>
+    <t>27,37.5</t>
+  </si>
+  <si>
+    <t>50,48.8</t>
+  </si>
+  <si>
+    <t>32,41.1</t>
+  </si>
+  <si>
+    <t>65,58.4</t>
+  </si>
+  <si>
+    <t>37,44.7</t>
+  </si>
+  <si>
+    <t>21,31.6</t>
+  </si>
+  <si>
+    <t>53,49.4</t>
+  </si>
+  <si>
+    <t>28,38.9</t>
+  </si>
+  <si>
+    <t>58,53.5</t>
+  </si>
+  <si>
+    <t>42,46.2</t>
+  </si>
+  <si>
+    <t>19,26.3</t>
+  </si>
+  <si>
+    <t>61,55.1</t>
+  </si>
+  <si>
+    <t>33,43.8</t>
+  </si>
+  <si>
+    <t>47,47.5</t>
+  </si>
+  <si>
+    <t>24,35.4</t>
+  </si>
+  <si>
+    <t>56,52.3</t>
+  </si>
+  <si>
+    <t>39,45.0</t>
+  </si>
+  <si>
+    <t>44,47.9</t>
+  </si>
+  <si>
+    <t>17,23.8</t>
+  </si>
+  <si>
+    <t>59,54.8</t>
+  </si>
+  <si>
+    <t>30,41.7</t>
+  </si>
+  <si>
+    <t>51,50.1</t>
+  </si>
+  <si>
+    <t>35,43.5</t>
+  </si>
+  <si>
+    <t>62,56.8</t>
+  </si>
+  <si>
+    <t>26,38.0</t>
+  </si>
+  <si>
+    <t>49,48.4</t>
+  </si>
+  <si>
+    <t>22,32.1</t>
+  </si>
+  <si>
+    <t>54,51.3</t>
+  </si>
+  <si>
+    <t>40,46.7</t>
+  </si>
+  <si>
+    <t>18,25.5</t>
+  </si>
+  <si>
+    <t>60,55.6</t>
+  </si>
+  <si>
+    <t>31,42.4</t>
+  </si>
+  <si>
+    <t>48,49.0</t>
+  </si>
+  <si>
+    <t>25,36.5</t>
   </si>
 </sst>
 </file>
@@ -1215,891 +1218,894 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1">
-        <v>111</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1">
-        <v>240</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1">
-        <v>56</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1">
-        <v>208</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1">
-        <v>275</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1">
-        <v>119</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1">
-        <v>215</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1">
-        <v>109</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1">
-        <v>260</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C11" s="1">
-        <v>176</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1">
-        <v>318</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C13" s="1">
-        <v>144</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1">
-        <v>273</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1">
-        <v>211</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1">
-        <v>327</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1">
-        <v>190</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="B18" s="2">
+        <v>49</v>
       </c>
       <c r="C18" s="1">
-        <v>286</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="B19" s="1">
+        <v>26</v>
       </c>
       <c r="C19" s="1">
-        <v>157</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="1">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1">
-        <v>331</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" s="1">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C21" s="1">
-        <v>225</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" s="1">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1">
-        <v>243</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1">
         <v>22</v>
       </c>
       <c r="C23" s="1">
-        <v>371</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1">
-        <v>221</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" s="1">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
-        <v>339</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="1">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C26" s="1">
-        <v>198</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1">
-        <v>384</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" s="1">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C28" s="1">
-        <v>278</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="1">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C29" s="1">
-        <v>374</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="1">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C30" s="1">
-        <v>235</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C31" s="1">
-        <v>353</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="1">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1">
-        <v>448</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1">
-        <v>297</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34" s="1">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C34" s="1">
-        <v>415</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35" s="1">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1">
-        <v>276</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" s="1">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C36" s="1">
-        <v>394</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="1">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C37" s="1">
-        <v>271</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1">
-        <v>428</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="1">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C39" s="1">
-        <v>355</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="1">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C40" s="1">
-        <v>473</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C41" s="1">
-        <v>323</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="1">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C42" s="1">
-        <v>441</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" s="1">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C43" s="1">
-        <v>290</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" s="1">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C44" s="1">
-        <v>486</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" s="1">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C45" s="1">
-        <v>380</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46" s="1">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C46" s="1">
-        <v>476</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C47" s="1">
-        <v>337</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48" s="1">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C48" s="1">
-        <v>455</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C49" s="1">
-        <v>393</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50" s="1">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C50" s="1">
-        <v>511</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C51" s="1">
-        <v>372</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" s="1">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C52" s="1">
-        <v>400</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53" s="1">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C53" s="1">
-        <v>564</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54" s="1">
         <v>53</v>
       </c>
       <c r="C54" s="1">
-        <v>434</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B55" s="1">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C55" s="1">
-        <v>563</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B56" s="1">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C56" s="1">
-        <v>457</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B57" s="1">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C57" s="1">
-        <v>542</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" s="1">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C58" s="1">
-        <v>414</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59" s="1">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C59" s="1">
-        <v>532</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" s="1">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C60" s="1">
-        <v>402</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C61" s="1">
-        <v>555</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" s="1">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="C62" s="1">
-        <v>449</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63" s="1">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C63" s="1">
-        <v>611</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" s="1">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C64" s="1">
-        <v>483</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" s="1">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C65" s="1">
-        <v>557</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" s="1">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="C66" s="1">
-        <v>484</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B67" s="1">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C67" s="1">
-        <v>624</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B68" s="1">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="C68" s="1">
-        <v>518</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B69" s="1">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C69" s="1">
-        <v>660</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B70" s="1">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C70" s="1">
-        <v>519</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B71" s="1">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C71" s="1">
-        <v>637</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B72" s="1">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="C72" s="1">
-        <v>487</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B73" s="1">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C73" s="1">
-        <v>616</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B74" s="1">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="C74" s="1">
-        <v>510</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B75" s="1">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C75" s="1">
-        <v>650</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B76" s="1">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="C76" s="1">
-        <v>577</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B77" s="1">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="C77" s="1">
-        <v>695</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B78" s="1">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C78" s="1">
-        <v>567</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B79" s="1">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C79" s="1">
-        <v>685</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B80" s="1">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C80" s="1">
-        <v>590</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B81" s="1">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C81" s="1">
-        <v>732</v>
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
